--- a/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 400 AHO QP COPART SR.xlsx
+++ b/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 400 AHO QP COPART SR.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Bocaiuva do Sul</t>
+          <t>Bocaiúva do Sul</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Itaperucu</t>
+          <t>Itaperuçu</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -16694,7 +16694,7 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -25454,7 +25454,7 @@
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
@@ -25562,7 +25562,7 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G441" s="2" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G442" s="2" t="inlineStr">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
@@ -25724,7 +25724,7 @@
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G445" s="2" t="inlineStr">
@@ -25832,7 +25832,7 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
@@ -26048,7 +26048,7 @@
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G451" s="2" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G452" s="2" t="inlineStr">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G453" s="2" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr">
@@ -26318,7 +26318,7 @@
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
@@ -26484,7 +26484,7 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
@@ -26542,7 +26542,7 @@
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G460" s="2" t="inlineStr">
@@ -26650,7 +26650,7 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G461" s="2" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
@@ -26812,7 +26812,7 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G464" s="2" t="inlineStr">
@@ -27050,7 +27050,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -27060,7 +27060,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -27170,7 +27170,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bocaiuva do Sul</t>
+          <t>Bocaiúva do Sul</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -27180,7 +27180,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Itaperucu</t>
+          <t>Itaperuçu</t>
         </is>
       </c>
       <c r="B34" t="n">

--- a/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 400 AHO QP COPART SR.xlsx
+++ b/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA 400 AHO QP COPART SR.xlsx
@@ -49,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6B4E"/>
+        <fgColor rgb="008E0E28"/>
       </patternFill>
     </fill>
   </fills>
